--- a/artfynd/A 62364-2023 artfynd.xlsx
+++ b/artfynd/A 62364-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122456438</v>
+        <v>122456368</v>
       </c>
       <c r="B2" t="n">
-        <v>55974</v>
+        <v>90819</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>206004</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gammbodarna, Gammbodarna, Ång</t>
+          <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585487</v>
+        <v>585537</v>
       </c>
       <c r="R2" t="n">
-        <v>7063694</v>
+        <v>7063656</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122456458</v>
+        <v>122456438</v>
       </c>
       <c r="B3" t="n">
-        <v>56584</v>
+        <v>55979</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,20 +799,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>206004</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -826,26 +821,21 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långmyran, Långmyran, Ång</t>
+          <t>Gammbodarna, Gammbodarna, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585469</v>
+        <v>585487</v>
       </c>
       <c r="R3" t="n">
-        <v>7063659</v>
+        <v>7063694</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122456368</v>
+        <v>122456458</v>
       </c>
       <c r="B4" t="n">
-        <v>90807</v>
+        <v>56589</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,38 +916,48 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585537</v>
+        <v>585469</v>
       </c>
       <c r="R4" t="n">
-        <v>7063656</v>
+        <v>7063659</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122456376</v>
+        <v>122456648</v>
       </c>
       <c r="B5" t="n">
-        <v>90785</v>
+        <v>90819</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,34 +1042,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långmyran, Långmyran, Ång</t>
+          <t>Gammbodarna, Gammbodarna, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585535</v>
+        <v>585191</v>
       </c>
       <c r="R5" t="n">
-        <v>7063656</v>
+        <v>7063555</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,22 +1126,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122456648</v>
+        <v>122456376</v>
       </c>
       <c r="B6" t="n">
-        <v>90819</v>
+        <v>90797</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,34 +1154,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gammbodarna, Gammbodarna, Ång</t>
+          <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585191</v>
+        <v>585535</v>
       </c>
       <c r="R6" t="n">
-        <v>7063555</v>
+        <v>7063656</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,12 +1238,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 62364-2023 artfynd.xlsx
+++ b/artfynd/A 62364-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122456368</v>
+        <v>122456458</v>
       </c>
       <c r="B2" t="n">
-        <v>90819</v>
+        <v>56589</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,48 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585537</v>
+        <v>585469</v>
       </c>
       <c r="R2" t="n">
-        <v>7063656</v>
+        <v>7063659</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +760,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +770,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122456438</v>
+        <v>122456368</v>
       </c>
       <c r="B3" t="n">
-        <v>55979</v>
+        <v>90826</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,39 +813,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>206004</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gammbodarna, Gammbodarna, Ång</t>
+          <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585487</v>
+        <v>585537</v>
       </c>
       <c r="R3" t="n">
-        <v>7063694</v>
+        <v>7063656</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122456458</v>
+        <v>122456376</v>
       </c>
       <c r="B4" t="n">
-        <v>56589</v>
+        <v>90804</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,48 +921,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585469</v>
+        <v>585535</v>
       </c>
       <c r="R4" t="n">
-        <v>7063659</v>
+        <v>7063656</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,7 +1024,7 @@
         <v>122456648</v>
       </c>
       <c r="B5" t="n">
-        <v>90819</v>
+        <v>90826</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1138,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122456376</v>
+        <v>122456438</v>
       </c>
       <c r="B6" t="n">
-        <v>90797</v>
+        <v>55979</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,34 +1149,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>206004</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Långmyran, Långmyran, Ång</t>
+          <t>Gammbodarna, Gammbodarna, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585535</v>
+        <v>585487</v>
       </c>
       <c r="R6" t="n">
-        <v>7063656</v>
+        <v>7063694</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 62364-2023 artfynd.xlsx
+++ b/artfynd/A 62364-2023 artfynd.xlsx
@@ -693,11 +693,6 @@
       <c r="E2" t="n">
         <v>100138</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Tjäder</t>
-        </is>
-      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>Tetrao urogallus</t>
@@ -797,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122456368</v>
+        <v>122456648</v>
       </c>
       <c r="B3" t="n">
-        <v>90826</v>
+        <v>90831</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,11 +810,6 @@
       <c r="E3" t="n">
         <v>5432</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>Porodaedalea chrysoloma</t>
@@ -833,14 +823,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långmyran, Långmyran, Ång</t>
+          <t>Gammbodarna, Gammbodarna, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585537</v>
+        <v>585191</v>
       </c>
       <c r="R3" t="n">
-        <v>7063656</v>
+        <v>7063555</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,22 +887,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122456376</v>
+        <v>122456438</v>
       </c>
       <c r="B4" t="n">
-        <v>90804</v>
+        <v>55979</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,34 +915,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Harticka</t>
-        </is>
+        <v>206004</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Långmyran, Långmyran, Ång</t>
+          <t>Gammbodarna, Gammbodarna, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585535</v>
+        <v>585487</v>
       </c>
       <c r="R4" t="n">
-        <v>7063656</v>
+        <v>7063694</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122456648</v>
+        <v>122456376</v>
       </c>
       <c r="B5" t="n">
-        <v>90826</v>
+        <v>90809</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,34 +1027,29 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
+        <v>1108</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gammbodarna, Gammbodarna, Ång</t>
+          <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585191</v>
+        <v>585535</v>
       </c>
       <c r="R5" t="n">
-        <v>7063555</v>
+        <v>7063656</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1081,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1091,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,22 +1106,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122456438</v>
+        <v>122456368</v>
       </c>
       <c r="B6" t="n">
-        <v>55979</v>
+        <v>90831</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,39 +1134,29 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>206004</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Skogshare</t>
-        </is>
+        <v>5432</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gammbodarna, Gammbodarna, Ång</t>
+          <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585487</v>
+        <v>585537</v>
       </c>
       <c r="R6" t="n">
-        <v>7063694</v>
+        <v>7063656</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,7 +1188,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1198,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 62364-2023 artfynd.xlsx
+++ b/artfynd/A 62364-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122456458</v>
+        <v>122456368</v>
       </c>
       <c r="B2" t="n">
-        <v>56589</v>
+        <v>90844</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,43 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>5432</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585469</v>
+        <v>585537</v>
       </c>
       <c r="R2" t="n">
-        <v>7063659</v>
+        <v>7063656</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122456648</v>
+        <v>122456458</v>
       </c>
       <c r="B3" t="n">
-        <v>90831</v>
+        <v>56593</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,33 +799,48 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100138</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gammbodarna, Gammbodarna, Ång</t>
+          <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585191</v>
+        <v>585469</v>
       </c>
       <c r="R3" t="n">
-        <v>7063555</v>
+        <v>7063659</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,22 +897,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122456438</v>
+        <v>122456376</v>
       </c>
       <c r="B4" t="n">
-        <v>55979</v>
+        <v>90822</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,34 +925,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>206004</v>
+        <v>1108</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gammbodarna, Gammbodarna, Ång</t>
+          <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585487</v>
+        <v>585535</v>
       </c>
       <c r="R4" t="n">
-        <v>7063694</v>
+        <v>7063656</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122456376</v>
+        <v>122456648</v>
       </c>
       <c r="B5" t="n">
-        <v>90809</v>
+        <v>90844</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,29 +1037,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>5432</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långmyran, Långmyran, Ång</t>
+          <t>Gammbodarna, Gammbodarna, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585535</v>
+        <v>585191</v>
       </c>
       <c r="R5" t="n">
-        <v>7063656</v>
+        <v>7063555</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1091,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1106,22 +1121,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122456368</v>
+        <v>122456438</v>
       </c>
       <c r="B6" t="n">
-        <v>90831</v>
+        <v>55983</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1134,29 +1149,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>206004</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Skogshare</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Långmyran, Långmyran, Ång</t>
+          <t>Gammbodarna, Gammbodarna, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585537</v>
+        <v>585487</v>
       </c>
       <c r="R6" t="n">
-        <v>7063656</v>
+        <v>7063694</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1188,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1198,7 +1223,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 62364-2023 artfynd.xlsx
+++ b/artfynd/A 62364-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122456368</v>
+        <v>122456648</v>
       </c>
       <c r="B2" t="n">
-        <v>90844</v>
+        <v>90857</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -711,14 +711,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Långmyran, Långmyran, Ång</t>
+          <t>Gammbodarna, Gammbodarna, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585537</v>
+        <v>585191</v>
       </c>
       <c r="R2" t="n">
-        <v>7063656</v>
+        <v>7063555</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,12 +775,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -912,7 +912,7 @@
         <v>122456376</v>
       </c>
       <c r="B4" t="n">
-        <v>90822</v>
+        <v>90835</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1021,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122456648</v>
+        <v>122456368</v>
       </c>
       <c r="B5" t="n">
-        <v>90844</v>
+        <v>90857</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1057,14 +1057,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gammbodarna, Gammbodarna, Ång</t>
+          <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585191</v>
+        <v>585537</v>
       </c>
       <c r="R5" t="n">
-        <v>7063555</v>
+        <v>7063656</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,12 +1121,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 62364-2023 artfynd.xlsx
+++ b/artfynd/A 62364-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122456648</v>
+        <v>122456368</v>
       </c>
       <c r="B2" t="n">
         <v>90857</v>
@@ -711,14 +711,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gammbodarna, Gammbodarna, Ång</t>
+          <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585191</v>
+        <v>585537</v>
       </c>
       <c r="R2" t="n">
-        <v>7063555</v>
+        <v>7063656</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +775,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122456458</v>
+        <v>122456376</v>
       </c>
       <c r="B3" t="n">
-        <v>56593</v>
+        <v>90835</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,48 +799,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585469</v>
+        <v>585535</v>
       </c>
       <c r="R3" t="n">
-        <v>7063659</v>
+        <v>7063656</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122456376</v>
+        <v>122456438</v>
       </c>
       <c r="B4" t="n">
-        <v>90835</v>
+        <v>55983</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,34 +915,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>206004</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Långmyran, Långmyran, Ång</t>
+          <t>Gammbodarna, Gammbodarna, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585535</v>
+        <v>585487</v>
       </c>
       <c r="R4" t="n">
-        <v>7063656</v>
+        <v>7063694</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122456368</v>
+        <v>122456458</v>
       </c>
       <c r="B5" t="n">
-        <v>90857</v>
+        <v>56593</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,38 +1028,48 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585537</v>
+        <v>585469</v>
       </c>
       <c r="R5" t="n">
-        <v>7063656</v>
+        <v>7063659</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122456438</v>
+        <v>122456648</v>
       </c>
       <c r="B6" t="n">
-        <v>55983</v>
+        <v>90857</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,39 +1154,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>206004</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gammbodarna, Gammbodarna, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585487</v>
+        <v>585191</v>
       </c>
       <c r="R6" t="n">
-        <v>7063694</v>
+        <v>7063555</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,12 +1238,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 62364-2023 artfynd.xlsx
+++ b/artfynd/A 62364-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122456368</v>
+        <v>122456458</v>
       </c>
       <c r="B2" t="n">
-        <v>90857</v>
+        <v>56593</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,48 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585537</v>
+        <v>585469</v>
       </c>
       <c r="R2" t="n">
-        <v>7063656</v>
+        <v>7063659</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +760,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +770,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,7 +800,7 @@
         <v>122456376</v>
       </c>
       <c r="B3" t="n">
-        <v>90835</v>
+        <v>90829</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -899,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122456438</v>
+        <v>122456368</v>
       </c>
       <c r="B4" t="n">
-        <v>55983</v>
+        <v>90851</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,39 +925,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>206004</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gammbodarna, Gammbodarna, Ång</t>
+          <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585487</v>
+        <v>585537</v>
       </c>
       <c r="R4" t="n">
-        <v>7063694</v>
+        <v>7063656</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122456458</v>
+        <v>122456438</v>
       </c>
       <c r="B5" t="n">
-        <v>56593</v>
+        <v>55983</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,20 +1033,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>206004</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1050,26 +1055,21 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långmyran, Långmyran, Ång</t>
+          <t>Gammbodarna, Gammbodarna, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585469</v>
+        <v>585487</v>
       </c>
       <c r="R5" t="n">
-        <v>7063659</v>
+        <v>7063694</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1141,7 +1141,7 @@
         <v>122456648</v>
       </c>
       <c r="B6" t="n">
-        <v>90857</v>
+        <v>90851</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 62364-2023 artfynd.xlsx
+++ b/artfynd/A 62364-2023 artfynd.xlsx
@@ -797,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122456376</v>
+        <v>122456438</v>
       </c>
       <c r="B3" t="n">
-        <v>90829</v>
+        <v>55983</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,34 +813,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>206004</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långmyran, Långmyran, Ång</t>
+          <t>Gammbodarna, Gammbodarna, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585535</v>
+        <v>585487</v>
       </c>
       <c r="R3" t="n">
-        <v>7063656</v>
+        <v>7063694</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +887,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,7 +914,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122456368</v>
+        <v>122456648</v>
       </c>
       <c r="B4" t="n">
         <v>90851</v>
@@ -945,14 +950,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Långmyran, Långmyran, Ång</t>
+          <t>Gammbodarna, Gammbodarna, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585537</v>
+        <v>585191</v>
       </c>
       <c r="R4" t="n">
-        <v>7063656</v>
+        <v>7063555</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,22 +1014,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122456438</v>
+        <v>122456376</v>
       </c>
       <c r="B5" t="n">
-        <v>55983</v>
+        <v>90829</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,39 +1042,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>206004</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gammbodarna, Gammbodarna, Ång</t>
+          <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585487</v>
+        <v>585535</v>
       </c>
       <c r="R5" t="n">
-        <v>7063694</v>
+        <v>7063656</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,7 +1138,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122456648</v>
+        <v>122456368</v>
       </c>
       <c r="B6" t="n">
         <v>90851</v>
@@ -1174,14 +1174,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gammbodarna, Gammbodarna, Ång</t>
+          <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585191</v>
+        <v>585537</v>
       </c>
       <c r="R6" t="n">
-        <v>7063555</v>
+        <v>7063656</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,12 +1238,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 62364-2023 artfynd.xlsx
+++ b/artfynd/A 62364-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122456458</v>
+        <v>122456376</v>
       </c>
       <c r="B2" t="n">
-        <v>56593</v>
+        <v>90830</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,48 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585469</v>
+        <v>585535</v>
       </c>
       <c r="R2" t="n">
-        <v>7063659</v>
+        <v>7063656</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -770,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122456438</v>
+        <v>122456458</v>
       </c>
       <c r="B3" t="n">
-        <v>55983</v>
+        <v>56594</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -809,20 +799,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>206004</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -831,21 +821,26 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gammbodarna, Gammbodarna, Ång</t>
+          <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585487</v>
+        <v>585469</v>
       </c>
       <c r="R3" t="n">
-        <v>7063694</v>
+        <v>7063659</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122456648</v>
+        <v>122456438</v>
       </c>
       <c r="B4" t="n">
-        <v>90851</v>
+        <v>55984</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,34 +925,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>206004</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gammbodarna, Gammbodarna, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585191</v>
+        <v>585487</v>
       </c>
       <c r="R4" t="n">
-        <v>7063555</v>
+        <v>7063694</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,22 +1014,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122456376</v>
+        <v>122456368</v>
       </c>
       <c r="B5" t="n">
-        <v>90829</v>
+        <v>90852</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,21 +1042,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,7 +1066,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585535</v>
+        <v>585537</v>
       </c>
       <c r="R5" t="n">
         <v>7063656</v>
@@ -1138,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122456368</v>
+        <v>122456648</v>
       </c>
       <c r="B6" t="n">
-        <v>90851</v>
+        <v>90852</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1174,14 +1174,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Långmyran, Långmyran, Ång</t>
+          <t>Gammbodarna, Gammbodarna, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585537</v>
+        <v>585191</v>
       </c>
       <c r="R6" t="n">
-        <v>7063656</v>
+        <v>7063555</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,12 +1238,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 62364-2023 artfynd.xlsx
+++ b/artfynd/A 62364-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122456376</v>
+        <v>122456648</v>
       </c>
       <c r="B2" t="n">
-        <v>90830</v>
+        <v>90855</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Långmyran, Långmyran, Ång</t>
+          <t>Gammbodarna, Gammbodarna, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585535</v>
+        <v>585191</v>
       </c>
       <c r="R2" t="n">
-        <v>7063656</v>
+        <v>7063555</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +775,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122456458</v>
+        <v>122456438</v>
       </c>
       <c r="B3" t="n">
-        <v>56594</v>
+        <v>55984</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,20 +799,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>206004</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -821,26 +821,21 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långmyran, Långmyran, Ång</t>
+          <t>Gammbodarna, Gammbodarna, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585469</v>
+        <v>585487</v>
       </c>
       <c r="R3" t="n">
-        <v>7063659</v>
+        <v>7063694</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122456438</v>
+        <v>122456368</v>
       </c>
       <c r="B4" t="n">
-        <v>55984</v>
+        <v>90855</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,39 +920,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>206004</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gammbodarna, Gammbodarna, Ång</t>
+          <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585487</v>
+        <v>585537</v>
       </c>
       <c r="R4" t="n">
-        <v>7063694</v>
+        <v>7063656</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122456368</v>
+        <v>122456458</v>
       </c>
       <c r="B5" t="n">
-        <v>90852</v>
+        <v>56594</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1038,38 +1028,48 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585537</v>
+        <v>585469</v>
       </c>
       <c r="R5" t="n">
-        <v>7063656</v>
+        <v>7063659</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122456648</v>
+        <v>122456376</v>
       </c>
       <c r="B6" t="n">
-        <v>90852</v>
+        <v>90833</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,34 +1154,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gammbodarna, Gammbodarna, Ång</t>
+          <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585191</v>
+        <v>585535</v>
       </c>
       <c r="R6" t="n">
-        <v>7063555</v>
+        <v>7063656</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,12 +1238,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 62364-2023 artfynd.xlsx
+++ b/artfynd/A 62364-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122456648</v>
+        <v>122456376</v>
       </c>
       <c r="B2" t="n">
-        <v>90855</v>
+        <v>90833</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gammbodarna, Gammbodarna, Ång</t>
+          <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585191</v>
+        <v>585535</v>
       </c>
       <c r="R2" t="n">
-        <v>7063555</v>
+        <v>7063656</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +775,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122456438</v>
+        <v>122456368</v>
       </c>
       <c r="B3" t="n">
-        <v>55984</v>
+        <v>90855</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,39 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>206004</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gammbodarna, Gammbodarna, Ång</t>
+          <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585487</v>
+        <v>585537</v>
       </c>
       <c r="R3" t="n">
-        <v>7063694</v>
+        <v>7063656</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122456368</v>
+        <v>122456438</v>
       </c>
       <c r="B4" t="n">
-        <v>90855</v>
+        <v>55984</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,34 +915,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>206004</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Långmyran, Långmyran, Ång</t>
+          <t>Gammbodarna, Gammbodarna, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585537</v>
+        <v>585487</v>
       </c>
       <c r="R4" t="n">
-        <v>7063656</v>
+        <v>7063694</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1138,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122456376</v>
+        <v>122456648</v>
       </c>
       <c r="B6" t="n">
-        <v>90833</v>
+        <v>90855</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,34 +1154,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Långmyran, Långmyran, Ång</t>
+          <t>Gammbodarna, Gammbodarna, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585535</v>
+        <v>585191</v>
       </c>
       <c r="R6" t="n">
-        <v>7063656</v>
+        <v>7063555</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,12 +1238,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 62364-2023 artfynd.xlsx
+++ b/artfynd/A 62364-2023 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122456376</v>
+        <v>122456368</v>
       </c>
       <c r="B3" t="n">
-        <v>90936</v>
+        <v>90962</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,21 +808,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,7 +832,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585535</v>
+        <v>585537</v>
       </c>
       <c r="R3" t="n">
         <v>7063656</v>
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122456458</v>
+        <v>122456376</v>
       </c>
       <c r="B4" t="n">
-        <v>56688</v>
+        <v>90940</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,48 +916,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585469</v>
+        <v>585535</v>
       </c>
       <c r="R4" t="n">
-        <v>7063659</v>
+        <v>7063656</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,7 +1019,7 @@
         <v>122456648</v>
       </c>
       <c r="B5" t="n">
-        <v>90958</v>
+        <v>90962</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1138,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122456368</v>
+        <v>122456458</v>
       </c>
       <c r="B6" t="n">
-        <v>90958</v>
+        <v>56688</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1150,38 +1140,48 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585537</v>
+        <v>585469</v>
       </c>
       <c r="R6" t="n">
-        <v>7063656</v>
+        <v>7063659</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 62364-2023 artfynd.xlsx
+++ b/artfynd/A 62364-2023 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122456368</v>
+        <v>122456458</v>
       </c>
       <c r="B3" t="n">
-        <v>90962</v>
+        <v>56688</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,38 +804,48 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585537</v>
+        <v>585469</v>
       </c>
       <c r="R3" t="n">
-        <v>7063656</v>
+        <v>7063659</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +887,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122456376</v>
+        <v>122456368</v>
       </c>
       <c r="B4" t="n">
-        <v>90940</v>
+        <v>90962</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,21 +930,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -944,7 +954,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585535</v>
+        <v>585537</v>
       </c>
       <c r="R4" t="n">
         <v>7063656</v>
@@ -1128,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122456458</v>
+        <v>122456376</v>
       </c>
       <c r="B6" t="n">
-        <v>56688</v>
+        <v>90940</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,48 +1150,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långmyran, Långmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585469</v>
+        <v>585535</v>
       </c>
       <c r="R6" t="n">
-        <v>7063659</v>
+        <v>7063656</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD6" t="b">
